--- a/data/trans_orig/IP22-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IP22-Provincia-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>34427</t>
+          <t>34414</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>43703</t>
+          <t>44041</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>65,49%</t>
+          <t>65,47%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>83,14%</t>
+          <t>83,78%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>36630</t>
+          <t>36035</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>47716</t>
+          <t>47531</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>60,83%</t>
+          <t>59,84%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>79,24%</t>
+          <t>78,93%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>74522</t>
+          <t>73077</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>89445</t>
+          <t>88524</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>66,07%</t>
+          <t>64,79%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>79,31%</t>
+          <t>78,49%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>8865</t>
+          <t>8527</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>18141</t>
+          <t>18154</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>16,86%</t>
+          <t>16,22%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>34,51%</t>
+          <t>34,53%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>12501</t>
+          <t>12686</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>23587</t>
+          <t>24182</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>20,76%</t>
+          <t>21,07%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>39,17%</t>
+          <t>40,16%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>23340</t>
+          <t>24261</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>38263</t>
+          <t>39708</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>20,69%</t>
+          <t>21,51%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>33,93%</t>
+          <t>35,21%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>74175</t>
+          <t>74867</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>87392</t>
+          <t>87589</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>73,03%</t>
+          <t>73,72%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>86,05%</t>
+          <t>86,24%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>74099</t>
+          <t>74603</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>88843</t>
+          <t>89015</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>68,13%</t>
+          <t>68,6%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>81,69%</t>
+          <t>81,85%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>153064</t>
+          <t>153495</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>172562</t>
+          <t>172592</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>72,78%</t>
+          <t>72,98%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>82,05%</t>
+          <t>82,06%</t>
         </is>
       </c>
     </row>
@@ -1307,7 +1307,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3070</t>
+          <t>3029</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1322,7 +1322,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>642</t>
+          <t>643</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>5888</t>
+          <t>5296</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1357,7 +1357,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>650</t>
+          <t>646</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>6374</t>
+          <t>5833</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1392,7 +1392,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>2,77%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>13470</t>
+          <t>13685</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>26401</t>
+          <t>26017</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>13,26%</t>
+          <t>13,47%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>26,0%</t>
+          <t>25,62%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>17892</t>
+          <t>17796</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>32292</t>
+          <t>31451</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>16,45%</t>
+          <t>16,36%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>29,69%</t>
+          <t>28,92%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>34782</t>
+          <t>35524</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>54114</t>
+          <t>53762</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>16,54%</t>
+          <t>16,89%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>25,73%</t>
+          <t>25,56%</t>
         </is>
       </c>
     </row>
@@ -1645,12 +1645,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>46295</t>
+          <t>45809</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>57623</t>
+          <t>57525</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1660,12 +1660,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>68,49%</t>
+          <t>67,77%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>85,24%</t>
+          <t>85,1%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1680,12 +1680,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>47709</t>
+          <t>47539</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>59018</t>
+          <t>58931</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1695,12 +1695,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>67,84%</t>
+          <t>67,6%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>83,92%</t>
+          <t>83,8%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1715,12 +1715,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>97990</t>
+          <t>97759</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>114579</t>
+          <t>114259</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1730,12 +1730,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>71,05%</t>
+          <t>70,88%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>83,07%</t>
+          <t>82,84%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>9974</t>
+          <t>10072</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>21302</t>
+          <t>21788</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>14,76%</t>
+          <t>14,9%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>31,51%</t>
+          <t>32,23%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>11309</t>
+          <t>11396</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>22618</t>
+          <t>22788</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>16,08%</t>
+          <t>16,2%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>32,16%</t>
+          <t>32,4%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>23345</t>
+          <t>23665</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>39934</t>
+          <t>40165</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>16,93%</t>
+          <t>17,16%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>28,95%</t>
+          <t>29,12%</t>
         </is>
       </c>
     </row>
@@ -2101,12 +2101,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>52706</t>
+          <t>52893</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>64146</t>
+          <t>63718</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2116,12 +2116,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>70,41%</t>
+          <t>70,65%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>85,69%</t>
+          <t>85,12%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2136,12 +2136,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>55390</t>
+          <t>55482</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>66959</t>
+          <t>67682</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2151,12 +2151,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>70,02%</t>
+          <t>70,13%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>84,64%</t>
+          <t>85,55%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>111551</t>
+          <t>111195</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>128254</t>
+          <t>128624</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2186,12 +2186,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>72,45%</t>
+          <t>72,22%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>83,3%</t>
+          <t>83,54%</t>
         </is>
       </c>
     </row>
@@ -2327,12 +2327,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>10715</t>
+          <t>11143</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>22155</t>
+          <t>21968</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2342,12 +2342,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>14,31%</t>
+          <t>14,88%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>29,59%</t>
+          <t>29,35%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2362,12 +2362,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>12152</t>
+          <t>11429</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>23721</t>
+          <t>23629</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2377,12 +2377,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>15,36%</t>
+          <t>14,45%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>29,98%</t>
+          <t>29,87%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2397,12 +2397,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>25718</t>
+          <t>25348</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>42421</t>
+          <t>42777</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2412,12 +2412,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>16,46%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>27,55%</t>
+          <t>27,78%</t>
         </is>
       </c>
     </row>
@@ -2557,12 +2557,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>31666</t>
+          <t>31849</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>38660</t>
+          <t>38677</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2572,12 +2572,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>75,66%</t>
+          <t>76,1%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>92,37%</t>
+          <t>92,41%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2592,12 +2592,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>33863</t>
+          <t>34514</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>42071</t>
+          <t>42094</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2607,12 +2607,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>75,51%</t>
+          <t>76,97%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>93,82%</t>
+          <t>93,87%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>69046</t>
+          <t>69030</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>79335</t>
+          <t>78800</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2642,12 +2642,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>79,64%</t>
+          <t>79,62%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>91,51%</t>
+          <t>90,89%</t>
         </is>
       </c>
     </row>
@@ -2783,12 +2783,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>3192</t>
+          <t>3175</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>10186</t>
+          <t>10003</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2798,12 +2798,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>7,59%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>24,34%</t>
+          <t>23,9%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,12 +2818,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2772</t>
+          <t>2749</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>10980</t>
+          <t>10329</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2833,12 +2833,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>6,13%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>24,49%</t>
+          <t>23,03%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,12 +2853,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>7360</t>
+          <t>7895</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>17649</t>
+          <t>17665</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2868,12 +2868,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>9,11%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>20,36%</t>
+          <t>20,38%</t>
         </is>
       </c>
     </row>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>37564</t>
+          <t>37831</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>48160</t>
+          <t>48218</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3028,12 +3028,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>67,01%</t>
+          <t>67,49%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>85,92%</t>
+          <t>86,02%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3048,12 +3048,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>39166</t>
+          <t>39443</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>49755</t>
+          <t>49831</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>65,57%</t>
+          <t>66,03%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>83,3%</t>
+          <t>83,42%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3083,12 +3083,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>81181</t>
+          <t>80249</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>96016</t>
+          <t>95424</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3098,12 +3098,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>70,11%</t>
+          <t>69,31%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>82,92%</t>
+          <t>82,41%</t>
         </is>
       </c>
     </row>
@@ -3166,7 +3166,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>2754</t>
+          <t>3129</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3201,7 +3201,7 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>3128</t>
+          <t>3122</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3239,12 +3239,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>7895</t>
+          <t>7837</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>18491</t>
+          <t>18224</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3254,12 +3254,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>14,08%</t>
+          <t>13,98%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>32,99%</t>
+          <t>32,51%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3274,12 +3274,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>9570</t>
+          <t>9418</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>19643</t>
+          <t>19736</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3289,12 +3289,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>16,02%</t>
+          <t>15,77%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>32,88%</t>
+          <t>33,04%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3309,12 +3309,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>19578</t>
+          <t>19822</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>34200</t>
+          <t>34504</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>16,91%</t>
+          <t>17,12%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>29,54%</t>
+          <t>29,8%</t>
         </is>
       </c>
     </row>
@@ -3469,12 +3469,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>91070</t>
+          <t>90808</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>106732</t>
+          <t>106262</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3484,12 +3484,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>70,8%</t>
+          <t>70,6%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>82,98%</t>
+          <t>82,62%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3504,12 +3504,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>95815</t>
+          <t>95289</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>111612</t>
+          <t>111456</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3519,12 +3519,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>70,63%</t>
+          <t>70,24%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>82,28%</t>
+          <t>82,16%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3539,12 +3539,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>191957</t>
+          <t>190937</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>215013</t>
+          <t>213905</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3554,12 +3554,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>72,63%</t>
+          <t>72,25%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>81,36%</t>
+          <t>80,94%</t>
         </is>
       </c>
     </row>
@@ -3587,7 +3587,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3326</t>
+          <t>3656</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3602,7 +3602,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3657,7 +3657,7 @@
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>3334</t>
+          <t>3105</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3672,7 +3672,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,17%</t>
         </is>
       </c>
     </row>
@@ -3695,12 +3695,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>21500</t>
+          <t>21613</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>36765</t>
+          <t>36667</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3710,12 +3710,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>16,72%</t>
+          <t>16,8%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>28,58%</t>
+          <t>28,51%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3730,12 +3730,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>24043</t>
+          <t>24199</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>39840</t>
+          <t>40366</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3745,12 +3745,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>17,72%</t>
+          <t>17,84%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>29,37%</t>
+          <t>29,76%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>48582</t>
+          <t>49792</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>71792</t>
+          <t>72685</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3780,12 +3780,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>18,38%</t>
+          <t>18,84%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>27,17%</t>
+          <t>27,5%</t>
         </is>
       </c>
     </row>
@@ -3925,12 +3925,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>129922</t>
+          <t>130264</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>143678</t>
+          <t>144406</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3940,12 +3940,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>82,28%</t>
+          <t>82,5%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>90,99%</t>
+          <t>91,45%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3960,12 +3960,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>128904</t>
+          <t>129333</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>143914</t>
+          <t>143932</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3975,12 +3975,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>78,57%</t>
+          <t>78,83%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>87,72%</t>
+          <t>87,73%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3995,12 +3995,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>264819</t>
+          <t>264816</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>284359</t>
+          <t>284952</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -4015,7 +4015,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>88,32%</t>
+          <t>88,5%</t>
         </is>
       </c>
     </row>
@@ -4078,7 +4078,7 @@
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>3128</t>
+          <t>3714</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4093,7 +4093,7 @@
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4113,7 +4113,7 @@
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>3410</t>
+          <t>3405</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4151,12 +4151,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>14226</t>
+          <t>13498</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>27982</t>
+          <t>27640</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4166,12 +4166,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>9,01%</t>
+          <t>8,55%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>17,72%</t>
+          <t>17,5%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4186,12 +4186,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>19697</t>
+          <t>19825</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>34426</t>
+          <t>34349</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4201,12 +4201,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>12,01%</t>
+          <t>12,08%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>20,98%</t>
+          <t>20,94%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4221,12 +4221,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>36749</t>
+          <t>36261</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>56276</t>
+          <t>56609</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4236,12 +4236,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>11,41%</t>
+          <t>11,26%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>17,48%</t>
+          <t>17,58%</t>
         </is>
       </c>
     </row>
@@ -4381,12 +4381,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>532737</t>
+          <t>532651</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>566201</t>
+          <t>566210</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4396,7 +4396,7 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>78,23%</t>
+          <t>78,21%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
@@ -4416,12 +4416,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>547412</t>
+          <t>547601</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>582857</t>
+          <t>582686</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4431,12 +4431,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>75,75%</t>
+          <t>75,77%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>80,65%</t>
+          <t>80,63%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4451,12 +4451,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>1091840</t>
+          <t>1088057</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>1139182</t>
+          <t>1139560</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4466,12 +4466,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>77,78%</t>
+          <t>77,51%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>81,15%</t>
+          <t>81,18%</t>
         </is>
       </c>
     </row>
@@ -4499,7 +4499,7 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>4567</t>
+          <t>4208</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4514,7 +4514,7 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4529,12 +4529,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>1284</t>
+          <t>1286</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>7164</t>
+          <t>6608</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4549,7 +4549,7 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4564,12 +4564,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>1912</t>
+          <t>1872</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>8986</t>
+          <t>8936</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4579,7 +4579,7 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,13%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
@@ -4607,12 +4607,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>114159</t>
+          <t>113439</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>147599</t>
+          <t>147250</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4622,12 +4622,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>16,76%</t>
+          <t>16,66%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>21,67%</t>
+          <t>21,62%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>137001</t>
+          <t>136471</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>172167</t>
+          <t>171199</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4657,12 +4657,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>18,96%</t>
+          <t>18,88%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>23,82%</t>
+          <t>23,69%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>260816</t>
+          <t>259608</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>307581</t>
+          <t>310094</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4692,12 +4692,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>18,58%</t>
+          <t>18,49%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>21,91%</t>
+          <t>22,09%</t>
         </is>
       </c>
     </row>
@@ -5073,12 +5073,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>33899</t>
+          <t>34001</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>44865</t>
+          <t>45150</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5088,12 +5088,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>59,03%</t>
+          <t>59,21%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>78,13%</t>
+          <t>78,62%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5108,12 +5108,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>27372</t>
+          <t>27421</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>40957</t>
+          <t>40879</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5123,12 +5123,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>43,4%</t>
+          <t>43,48%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>64,94%</t>
+          <t>64,82%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5143,12 +5143,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>66162</t>
+          <t>64934</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>84049</t>
+          <t>82666</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>54,91%</t>
+          <t>53,89%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>69,76%</t>
+          <t>68,61%</t>
         </is>
       </c>
     </row>
@@ -5191,7 +5191,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2931</t>
+          <t>2937</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5206,7 +5206,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5221,12 +5221,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>565</t>
+          <t>574</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>5411</t>
+          <t>5558</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5236,12 +5236,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>8,81%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5256,12 +5256,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>603</t>
+          <t>577</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>5809</t>
+          <t>5966</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5271,12 +5271,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>4,95%</t>
         </is>
       </c>
     </row>
@@ -5299,12 +5299,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>11930</t>
+          <t>11702</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>22619</t>
+          <t>22977</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5314,12 +5314,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>20,77%</t>
+          <t>20,38%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>39,39%</t>
+          <t>40,01%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -5334,12 +5334,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>20156</t>
+          <t>20833</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>33879</t>
+          <t>33862</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5349,12 +5349,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>31,96%</t>
+          <t>33,03%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>53,72%</t>
+          <t>53,69%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5369,12 +5369,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>34848</t>
+          <t>35470</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>52371</t>
+          <t>52772</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5384,12 +5384,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>28,92%</t>
+          <t>29,44%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>43,46%</t>
+          <t>43,8%</t>
         </is>
       </c>
     </row>
@@ -5529,12 +5529,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>64144</t>
+          <t>62429</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>78864</t>
+          <t>77960</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5544,12 +5544,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>61,64%</t>
+          <t>59,99%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>75,78%</t>
+          <t>74,91%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5564,12 +5564,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>63654</t>
+          <t>61917</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>79203</t>
+          <t>79368</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5579,12 +5579,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>57,26%</t>
+          <t>55,7%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>71,25%</t>
+          <t>71,4%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5599,12 +5599,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>131066</t>
+          <t>130742</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>153163</t>
+          <t>153628</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5614,12 +5614,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>60,9%</t>
+          <t>60,75%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>71,16%</t>
+          <t>71,38%</t>
         </is>
       </c>
     </row>
@@ -5755,12 +5755,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>25204</t>
+          <t>26108</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>39924</t>
+          <t>41639</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5770,12 +5770,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>24,22%</t>
+          <t>25,09%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>38,36%</t>
+          <t>40,01%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5790,12 +5790,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>31956</t>
+          <t>31791</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>47505</t>
+          <t>49242</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5805,12 +5805,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>28,75%</t>
+          <t>28,6%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>42,74%</t>
+          <t>44,3%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5825,12 +5825,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>62064</t>
+          <t>61599</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>84161</t>
+          <t>84485</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>28,84%</t>
+          <t>28,62%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>39,1%</t>
+          <t>39,25%</t>
         </is>
       </c>
     </row>
@@ -5985,12 +5985,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>40608</t>
+          <t>40021</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>53128</t>
+          <t>52809</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6000,12 +6000,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>59,56%</t>
+          <t>58,7%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>77,93%</t>
+          <t>77,46%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6020,12 +6020,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>41373</t>
+          <t>41679</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>53974</t>
+          <t>54714</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6035,12 +6035,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>58,06%</t>
+          <t>58,49%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>75,75%</t>
+          <t>76,79%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6055,12 +6055,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>86043</t>
+          <t>86425</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>104644</t>
+          <t>104742</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6070,12 +6070,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>61,71%</t>
+          <t>61,98%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>75,05%</t>
+          <t>75,12%</t>
         </is>
       </c>
     </row>
@@ -6103,7 +6103,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4085</t>
+          <t>3448</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6118,7 +6118,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6138,7 +6138,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3496</t>
+          <t>4260</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6153,7 +6153,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6173,7 +6173,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>4778</t>
+          <t>5107</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6188,7 +6188,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,66%</t>
         </is>
       </c>
     </row>
@@ -6211,12 +6211,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>14402</t>
+          <t>14570</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>26627</t>
+          <t>26995</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>21,12%</t>
+          <t>21,37%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>39,05%</t>
+          <t>39,6%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6246,12 +6246,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>16346</t>
+          <t>16332</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>29327</t>
+          <t>29241</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>22,94%</t>
+          <t>22,92%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>41,16%</t>
+          <t>41,04%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6281,12 +6281,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>34180</t>
+          <t>33619</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>52527</t>
+          <t>51445</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>24,51%</t>
+          <t>24,11%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>37,67%</t>
+          <t>36,9%</t>
         </is>
       </c>
     </row>
@@ -6441,12 +6441,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>51503</t>
+          <t>51343</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>64603</t>
+          <t>64098</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6456,12 +6456,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>66,23%</t>
+          <t>66,03%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>83,08%</t>
+          <t>82,43%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>50174</t>
+          <t>50282</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>64777</t>
+          <t>64852</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6491,12 +6491,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>61,01%</t>
+          <t>61,14%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>78,77%</t>
+          <t>78,86%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6511,12 +6511,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>106356</t>
+          <t>106071</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>124860</t>
+          <t>124510</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6526,12 +6526,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>66,47%</t>
+          <t>66,3%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>78,04%</t>
+          <t>77,82%</t>
         </is>
       </c>
     </row>
@@ -6559,7 +6559,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>5655</t>
+          <t>4959</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6574,7 +6574,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>6,38%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6629,7 +6629,7 @@
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>5507</t>
+          <t>5612</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6644,7 +6644,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,51%</t>
         </is>
       </c>
     </row>
@@ -6667,12 +6667,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>12378</t>
+          <t>12736</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>25105</t>
+          <t>24847</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -6682,12 +6682,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>15,92%</t>
+          <t>16,38%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>32,29%</t>
+          <t>31,95%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>17457</t>
+          <t>17382</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>32060</t>
+          <t>31952</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6717,12 +6717,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>21,23%</t>
+          <t>21,14%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>38,99%</t>
+          <t>38,86%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6737,12 +6737,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>33817</t>
+          <t>33598</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>52293</t>
+          <t>51920</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6752,12 +6752,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>21,14%</t>
+          <t>21,0%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>32,68%</t>
+          <t>32,45%</t>
         </is>
       </c>
     </row>
@@ -6897,12 +6897,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>22316</t>
+          <t>22560</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>32854</t>
+          <t>32589</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6912,12 +6912,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>50,83%</t>
+          <t>51,39%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>74,84%</t>
+          <t>74,23%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6932,12 +6932,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>28797</t>
+          <t>28841</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>38631</t>
+          <t>38956</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6947,12 +6947,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>61,59%</t>
+          <t>61,69%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>82,63%</t>
+          <t>83,32%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6967,12 +6967,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>53656</t>
+          <t>54280</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>68431</t>
+          <t>68585</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6982,12 +6982,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>59,19%</t>
+          <t>59,88%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>75,49%</t>
+          <t>75,66%</t>
         </is>
       </c>
     </row>
@@ -7050,7 +7050,7 @@
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>3434</t>
+          <t>3435</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -7065,7 +7065,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>7,35%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -7085,7 +7085,7 @@
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>3410</t>
+          <t>4146</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -7100,7 +7100,7 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>4,57%</t>
         </is>
       </c>
     </row>
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>11047</t>
+          <t>11312</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>21585</t>
+          <t>21341</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7138,12 +7138,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>25,16%</t>
+          <t>25,77%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>49,17%</t>
+          <t>48,61%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7158,12 +7158,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>7434</t>
+          <t>7261</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>17289</t>
+          <t>17078</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7173,12 +7173,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>15,9%</t>
+          <t>15,53%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>36,98%</t>
+          <t>36,53%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7193,12 +7193,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>21169</t>
+          <t>21508</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>36372</t>
+          <t>35703</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7208,12 +7208,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>23,35%</t>
+          <t>23,73%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>40,12%</t>
+          <t>39,38%</t>
         </is>
       </c>
     </row>
@@ -7353,12 +7353,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>33110</t>
+          <t>33667</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>44555</t>
+          <t>44806</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -7368,12 +7368,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>59,14%</t>
+          <t>60,14%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>79,58%</t>
+          <t>80,03%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -7388,12 +7388,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>31558</t>
+          <t>31275</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>44478</t>
+          <t>44231</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -7403,12 +7403,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>53,04%</t>
+          <t>52,56%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>74,75%</t>
+          <t>74,33%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>68354</t>
+          <t>68990</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>86594</t>
+          <t>85767</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -7438,12 +7438,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>59,19%</t>
+          <t>59,74%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>74,98%</t>
+          <t>74,26%</t>
         </is>
       </c>
     </row>
@@ -7506,7 +7506,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>3928</t>
+          <t>3996</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -7521,7 +7521,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>6,72%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -7541,7 +7541,7 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>3935</t>
+          <t>3338</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -7556,7 +7556,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>2,89%</t>
         </is>
       </c>
     </row>
@@ -7579,12 +7579,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>11430</t>
+          <t>11179</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>22875</t>
+          <t>22318</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -7594,12 +7594,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>20,42%</t>
+          <t>19,97%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>40,86%</t>
+          <t>39,86%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -7614,12 +7614,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>14498</t>
+          <t>14606</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>27180</t>
+          <t>27275</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -7629,12 +7629,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>24,37%</t>
+          <t>24,55%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>45,68%</t>
+          <t>45,84%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -7649,12 +7649,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>28177</t>
+          <t>29436</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>46108</t>
+          <t>46028</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -7664,12 +7664,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>24,4%</t>
+          <t>25,49%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>39,92%</t>
+          <t>39,86%</t>
         </is>
       </c>
     </row>
@@ -7809,12 +7809,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>98132</t>
+          <t>97772</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>114585</t>
+          <t>115161</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7824,12 +7824,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>70,74%</t>
+          <t>70,48%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>82,6%</t>
+          <t>83,02%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7844,12 +7844,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>92918</t>
+          <t>91745</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>111563</t>
+          <t>110072</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7859,12 +7859,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>64,05%</t>
+          <t>63,24%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>76,9%</t>
+          <t>75,88%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7879,12 +7879,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>195633</t>
+          <t>197445</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>221252</t>
+          <t>221379</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7894,12 +7894,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>68,94%</t>
+          <t>69,57%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>77,96%</t>
+          <t>78,01%</t>
         </is>
       </c>
     </row>
@@ -7927,7 +7927,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3635</t>
+          <t>3623</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7942,7 +7942,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7962,7 +7962,7 @@
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>5941</t>
+          <t>6709</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7977,7 +7977,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7992,12 +7992,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>694</t>
+          <t>693</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>7341</t>
+          <t>6361</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -8012,7 +8012,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,24%</t>
         </is>
       </c>
     </row>
@@ -8035,12 +8035,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>23840</t>
+          <t>23074</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>39698</t>
+          <t>40267</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -8050,12 +8050,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>17,19%</t>
+          <t>16,63%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>28,62%</t>
+          <t>29,03%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -8070,12 +8070,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>31931</t>
+          <t>33524</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>50086</t>
+          <t>51850</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -8085,12 +8085,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>22,01%</t>
+          <t>23,11%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>34,53%</t>
+          <t>35,74%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -8105,12 +8105,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>60494</t>
+          <t>59622</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>85166</t>
+          <t>83760</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -8120,12 +8120,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>21,32%</t>
+          <t>21,01%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>30,01%</t>
+          <t>29,51%</t>
         </is>
       </c>
     </row>
@@ -8265,12 +8265,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>146385</t>
+          <t>146016</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>157407</t>
+          <t>156931</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -8280,12 +8280,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>88,88%</t>
+          <t>88,65%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>95,57%</t>
+          <t>95,28%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -8300,12 +8300,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>149507</t>
+          <t>149870</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>161532</t>
+          <t>161545</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -8315,12 +8315,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>87,27%</t>
+          <t>87,48%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>94,29%</t>
+          <t>94,3%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -8335,12 +8335,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>300793</t>
+          <t>300723</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>316521</t>
+          <t>316135</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -8350,12 +8350,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>89,52%</t>
+          <t>89,49%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>94,2%</t>
+          <t>94,08%</t>
         </is>
       </c>
     </row>
@@ -8383,7 +8383,7 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>2636</t>
+          <t>3205</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -8398,7 +8398,7 @@
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -8418,7 +8418,7 @@
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>3762</t>
+          <t>3339</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -8433,7 +8433,7 @@
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -8453,7 +8453,7 @@
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>4471</t>
+          <t>4990</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -8468,7 +8468,7 @@
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,48%</t>
         </is>
       </c>
     </row>
@@ -8491,12 +8491,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>6964</t>
+          <t>7469</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>17572</t>
+          <t>17573</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -8506,7 +8506,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -8526,12 +8526,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>9167</t>
+          <t>9031</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>21065</t>
+          <t>20802</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -8541,12 +8541,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,27%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>12,3%</t>
+          <t>12,14%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -8561,12 +8561,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>18664</t>
+          <t>18775</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>33920</t>
+          <t>34342</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -8576,12 +8576,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>10,09%</t>
+          <t>10,22%</t>
         </is>
       </c>
     </row>
@@ -8721,12 +8721,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>523584</t>
+          <t>523740</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>561139</t>
+          <t>562683</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -8736,12 +8736,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>73,67%</t>
+          <t>73,69%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>78,95%</t>
+          <t>79,17%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -8756,12 +8756,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>521519</t>
+          <t>522517</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>563002</t>
+          <t>563418</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -8771,12 +8771,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>69,5%</t>
+          <t>69,64%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>75,03%</t>
+          <t>75,09%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -8791,12 +8791,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>1056984</t>
+          <t>1057381</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>1114274</t>
+          <t>1112764</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -8806,12 +8806,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>72,34%</t>
+          <t>72,37%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>76,26%</t>
+          <t>76,16%</t>
         </is>
       </c>
     </row>
@@ -8834,12 +8834,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>1705</t>
+          <t>1602</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>8756</t>
+          <t>8262</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -8849,12 +8849,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -8869,12 +8869,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>3304</t>
+          <t>3144</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>11505</t>
+          <t>12256</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -8884,12 +8884,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -8904,12 +8904,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>6180</t>
+          <t>6242</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>17435</t>
+          <t>17235</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -8919,12 +8919,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,18%</t>
         </is>
       </c>
     </row>
@@ -8947,12 +8947,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>145830</t>
+          <t>144218</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>183558</t>
+          <t>182195</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -8962,12 +8962,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>20,52%</t>
+          <t>20,29%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>25,83%</t>
+          <t>25,63%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -8982,12 +8982,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>181402</t>
+          <t>181662</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>222058</t>
+          <t>221723</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -8997,12 +8997,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>24,18%</t>
+          <t>24,21%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>29,59%</t>
+          <t>29,55%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -9017,12 +9017,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>336866</t>
+          <t>338655</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>393635</t>
+          <t>393261</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -9032,12 +9032,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>23,06%</t>
+          <t>23,18%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>26,94%</t>
+          <t>26,92%</t>
         </is>
       </c>
     </row>
@@ -9413,12 +9413,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>30085</t>
+          <t>29898</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>41737</t>
+          <t>41503</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -9428,12 +9428,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>52,44%</t>
+          <t>52,11%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>72,75%</t>
+          <t>72,34%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9448,12 +9448,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>36542</t>
+          <t>35935</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>49520</t>
+          <t>48790</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -9463,12 +9463,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>56,69%</t>
+          <t>55,75%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>76,82%</t>
+          <t>75,69%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9483,12 +9483,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>69913</t>
+          <t>70241</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>87099</t>
+          <t>87568</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -9498,12 +9498,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>57,38%</t>
+          <t>57,65%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>71,49%</t>
+          <t>71,88%</t>
         </is>
       </c>
     </row>
@@ -9531,7 +9531,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2760</t>
+          <t>3132</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -9546,7 +9546,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9601,7 +9601,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>2693</t>
+          <t>2686</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -9616,7 +9616,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,2%</t>
         </is>
       </c>
     </row>
@@ -9639,12 +9639,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>15165</t>
+          <t>15200</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>26700</t>
+          <t>26968</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -9654,12 +9654,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>26,43%</t>
+          <t>26,49%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>46,54%</t>
+          <t>47,01%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -9674,12 +9674,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>14942</t>
+          <t>15672</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>27920</t>
+          <t>28527</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -9689,12 +9689,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>23,18%</t>
+          <t>24,31%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>43,31%</t>
+          <t>44,25%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -9709,12 +9709,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>34319</t>
+          <t>33861</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>51559</t>
+          <t>51574</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -9724,12 +9724,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>28,17%</t>
+          <t>27,79%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>42,32%</t>
+          <t>42,33%</t>
         </is>
       </c>
     </row>
@@ -9869,12 +9869,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>67878</t>
+          <t>67928</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>82519</t>
+          <t>81459</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -9884,12 +9884,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>65,3%</t>
+          <t>65,35%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>79,39%</t>
+          <t>78,37%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9904,12 +9904,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>74273</t>
+          <t>73760</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>88908</t>
+          <t>89622</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -9919,12 +9919,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>67,35%</t>
+          <t>66,88%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>80,62%</t>
+          <t>81,27%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9939,12 +9939,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>145829</t>
+          <t>145621</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>166005</t>
+          <t>166457</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -9954,12 +9954,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>68,07%</t>
+          <t>67,97%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>77,49%</t>
+          <t>77,7%</t>
         </is>
       </c>
     </row>
@@ -10095,12 +10095,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>21428</t>
+          <t>22488</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>36069</t>
+          <t>36019</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -10110,12 +10110,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>20,61%</t>
+          <t>21,63%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>34,7%</t>
+          <t>34,65%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10130,12 +10130,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>21375</t>
+          <t>20661</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>36010</t>
+          <t>36523</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -10145,12 +10145,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>19,38%</t>
+          <t>18,73%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>32,65%</t>
+          <t>33,12%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10165,12 +10165,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>48225</t>
+          <t>47773</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>68401</t>
+          <t>68609</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -10180,12 +10180,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>22,51%</t>
+          <t>22,3%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>31,93%</t>
+          <t>32,03%</t>
         </is>
       </c>
     </row>
@@ -10325,12 +10325,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>55951</t>
+          <t>56107</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>63956</t>
+          <t>63971</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -10340,12 +10340,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>83,72%</t>
+          <t>83,95%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>95,7%</t>
+          <t>95,72%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -10360,12 +10360,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>62549</t>
+          <t>63010</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>69166</t>
+          <t>69188</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -10375,12 +10375,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>89,48%</t>
+          <t>90,14%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>98,94%</t>
+          <t>98,97%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -10395,12 +10395,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>122224</t>
+          <t>121180</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>131711</t>
+          <t>131492</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -10410,12 +10410,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>89,39%</t>
+          <t>88,62%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>96,33%</t>
+          <t>96,17%</t>
         </is>
       </c>
     </row>
@@ -10438,12 +10438,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2121</t>
+          <t>2062</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>9368</t>
+          <t>8786</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -10453,12 +10453,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>14,02%</t>
+          <t>13,15%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10478,7 +10478,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3366</t>
+          <t>3494</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -10493,7 +10493,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10508,12 +10508,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2082</t>
+          <t>2190</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>9332</t>
+          <t>9938</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -10523,12 +10523,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>7,27%</t>
         </is>
       </c>
     </row>
@@ -10556,7 +10556,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>5243</t>
+          <t>5175</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -10571,7 +10571,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>7,85%</t>
+          <t>7,74%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10586,12 +10586,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>720</t>
+          <t>713</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>6386</t>
+          <t>6372</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -10601,12 +10601,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>9,14%</t>
+          <t>9,12%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10626,7 +10626,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>9170</t>
+          <t>8411</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -10641,7 +10641,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>6,15%</t>
         </is>
       </c>
     </row>
@@ -10781,12 +10781,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>50598</t>
+          <t>50999</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>62265</t>
+          <t>63022</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10796,12 +10796,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>65,74%</t>
+          <t>66,27%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>80,9%</t>
+          <t>81,89%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10816,12 +10816,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>45837</t>
+          <t>44137</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>60606</t>
+          <t>59431</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -10831,12 +10831,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>57,04%</t>
+          <t>54,92%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>75,41%</t>
+          <t>73,95%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10851,12 +10851,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>99697</t>
+          <t>100279</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>119606</t>
+          <t>118996</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -10866,12 +10866,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>63,37%</t>
+          <t>63,74%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>76,02%</t>
+          <t>75,64%</t>
         </is>
       </c>
     </row>
@@ -10899,7 +10899,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3765</t>
+          <t>3803</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -10914,7 +10914,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10934,7 +10934,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3157</t>
+          <t>4334</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -10949,7 +10949,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>5,39%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10969,7 +10969,7 @@
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>4674</t>
+          <t>4591</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10984,7 +10984,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>2,92%</t>
         </is>
       </c>
     </row>
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>14075</t>
+          <t>13387</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>25566</t>
+          <t>24889</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -11022,12 +11022,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>18,29%</t>
+          <t>17,39%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>33,22%</t>
+          <t>32,34%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -11042,12 +11042,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>19062</t>
+          <t>19981</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>33840</t>
+          <t>35370</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -11057,12 +11057,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>23,72%</t>
+          <t>24,86%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>42,11%</t>
+          <t>44,01%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -11077,12 +11077,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>36667</t>
+          <t>36925</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>56046</t>
+          <t>55791</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -11092,12 +11092,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>23,31%</t>
+          <t>23,47%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>35,62%</t>
+          <t>35,46%</t>
         </is>
       </c>
     </row>
@@ -11237,12 +11237,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>34571</t>
+          <t>34507</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>41368</t>
+          <t>41585</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -11252,12 +11252,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>79,59%</t>
+          <t>79,44%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>95,23%</t>
+          <t>95,73%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11272,7 +11272,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>42038</t>
+          <t>42132</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -11287,7 +11287,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>90,7%</t>
+          <t>90,9%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -11307,12 +11307,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>78727</t>
+          <t>79564</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>86795</t>
+          <t>87128</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -11322,12 +11322,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>87,68%</t>
+          <t>88,61%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>96,67%</t>
+          <t>97,04%</t>
         </is>
       </c>
     </row>
@@ -11463,12 +11463,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2070</t>
+          <t>1853</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>8867</t>
+          <t>8931</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -11478,12 +11478,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>20,41%</t>
+          <t>20,56%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11503,7 +11503,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>4312</t>
+          <t>4218</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -11518,7 +11518,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>9,3%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11533,12 +11533,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2993</t>
+          <t>2660</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>11061</t>
+          <t>10224</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -11548,12 +11548,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>12,32%</t>
+          <t>11,39%</t>
         </is>
       </c>
     </row>
@@ -11693,12 +11693,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>36720</t>
+          <t>36343</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>46833</t>
+          <t>46785</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -11708,12 +11708,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>67,66%</t>
+          <t>66,96%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>86,29%</t>
+          <t>86,2%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -11728,12 +11728,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>43465</t>
+          <t>43600</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>52655</t>
+          <t>53049</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -11743,12 +11743,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>75,28%</t>
+          <t>75,51%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>91,19%</t>
+          <t>91,88%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -11763,12 +11763,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>82950</t>
+          <t>82457</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>97032</t>
+          <t>97339</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -11778,12 +11778,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>74,05%</t>
+          <t>73,61%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>86,63%</t>
+          <t>86,9%</t>
         </is>
       </c>
     </row>
@@ -11919,12 +11919,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>7440</t>
+          <t>7488</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>17553</t>
+          <t>17930</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -11934,12 +11934,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>13,71%</t>
+          <t>13,8%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>32,34%</t>
+          <t>33,04%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -11954,12 +11954,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>5084</t>
+          <t>4690</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>14274</t>
+          <t>14139</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -11969,12 +11969,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>8,81%</t>
+          <t>8,12%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>24,72%</t>
+          <t>24,49%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -11989,12 +11989,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>14980</t>
+          <t>14673</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>29062</t>
+          <t>29555</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -12004,12 +12004,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>13,37%</t>
+          <t>13,1%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>25,95%</t>
+          <t>26,39%</t>
         </is>
       </c>
     </row>
@@ -12149,12 +12149,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>115291</t>
+          <t>115441</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>127427</t>
+          <t>127268</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -12164,12 +12164,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>83,93%</t>
+          <t>84,03%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>92,76%</t>
+          <t>92,64%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -12184,12 +12184,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>126898</t>
+          <t>127164</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>137448</t>
+          <t>136993</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -12199,12 +12199,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>88,08%</t>
+          <t>88,26%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>95,4%</t>
+          <t>95,09%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -12219,12 +12219,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>246486</t>
+          <t>247321</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>261965</t>
+          <t>262350</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -12234,12 +12234,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>87,58%</t>
+          <t>87,88%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>93,08%</t>
+          <t>93,21%</t>
         </is>
       </c>
     </row>
@@ -12267,7 +12267,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>4452</t>
+          <t>4489</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -12282,7 +12282,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -12302,7 +12302,7 @@
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>2970</t>
+          <t>2644</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -12317,7 +12317,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -12332,12 +12332,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>525</t>
+          <t>524</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>5070</t>
+          <t>4523</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -12352,7 +12352,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,61%</t>
         </is>
       </c>
     </row>
@@ -12375,12 +12375,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>8827</t>
+          <t>9109</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>20594</t>
+          <t>20630</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -12390,12 +12390,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,63%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>14,99%</t>
+          <t>15,02%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -12410,12 +12410,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>6502</t>
+          <t>6474</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>16889</t>
+          <t>16366</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -12425,12 +12425,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>11,72%</t>
+          <t>11,36%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -12445,12 +12445,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>17446</t>
+          <t>17407</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>32599</t>
+          <t>31998</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -12460,12 +12460,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>6,18%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>11,58%</t>
+          <t>11,37%</t>
         </is>
       </c>
     </row>
@@ -12605,12 +12605,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>141125</t>
+          <t>141307</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>152993</t>
+          <t>153226</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -12620,12 +12620,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>85,96%</t>
+          <t>86,07%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>93,19%</t>
+          <t>93,33%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -12640,12 +12640,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>140875</t>
+          <t>140901</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>155002</t>
+          <t>155099</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -12655,12 +12655,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>82,46%</t>
+          <t>82,47%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>90,72%</t>
+          <t>90,78%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -12675,12 +12675,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>286396</t>
+          <t>286929</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>304570</t>
+          <t>305232</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -12690,12 +12690,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>85,49%</t>
+          <t>85,64%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>90,91%</t>
+          <t>91,11%</t>
         </is>
       </c>
     </row>
@@ -12723,7 +12723,7 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>3986</t>
+          <t>3451</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -12738,7 +12738,7 @@
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -12758,7 +12758,7 @@
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>5474</t>
+          <t>4634</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -12773,7 +12773,7 @@
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -12788,12 +12788,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>623</t>
+          <t>630</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>5573</t>
+          <t>6922</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -12808,7 +12808,7 @@
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>2,07%</t>
         </is>
       </c>
     </row>
@@ -12831,12 +12831,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>10471</t>
+          <t>10505</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>22091</t>
+          <t>22314</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -12846,12 +12846,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>6,4%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>13,46%</t>
+          <t>13,59%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -12866,12 +12866,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>14150</t>
+          <t>14476</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>28152</t>
+          <t>28181</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -12881,12 +12881,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>8,28%</t>
+          <t>8,47%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>16,48%</t>
+          <t>16,49%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -12901,12 +12901,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>28299</t>
+          <t>27594</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>46286</t>
+          <t>45743</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -12916,12 +12916,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>8,24%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>13,82%</t>
+          <t>13,65%</t>
         </is>
       </c>
     </row>
@@ -13061,12 +13061,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>561168</t>
+          <t>564245</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>594746</t>
+          <t>595776</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -13076,12 +13076,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>79,67%</t>
+          <t>80,11%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>84,44%</t>
+          <t>84,58%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -13096,12 +13096,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>601367</t>
+          <t>602335</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>635723</t>
+          <t>635749</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -13111,12 +13111,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>80,83%</t>
+          <t>80,96%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>85,44%</t>
+          <t>85,45%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -13131,12 +13131,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>1175115</t>
+          <t>1176799</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>1220500</t>
+          <t>1224153</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -13146,12 +13146,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>81,13%</t>
+          <t>81,25%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>84,27%</t>
+          <t>84,52%</t>
         </is>
       </c>
     </row>
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>4187</t>
+          <t>4018</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>13289</t>
+          <t>13137</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -13189,12 +13189,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -13209,12 +13209,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>1286</t>
+          <t>1051</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>8201</t>
+          <t>7293</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -13224,12 +13224,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -13244,12 +13244,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>6877</t>
+          <t>5831</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>18203</t>
+          <t>16637</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -13259,12 +13259,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,15%</t>
         </is>
       </c>
     </row>
@@ -13287,12 +13287,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>102190</t>
+          <t>101910</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>134076</t>
+          <t>131857</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -13302,12 +13302,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>14,51%</t>
+          <t>14,47%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>19,03%</t>
+          <t>18,72%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -13322,12 +13322,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>105714</t>
+          <t>105517</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>139984</t>
+          <t>138030</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -13337,12 +13337,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>14,21%</t>
+          <t>14,18%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>18,81%</t>
+          <t>18,55%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -13357,12 +13357,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>216644</t>
+          <t>214536</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>262404</t>
+          <t>260543</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -13372,12 +13372,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>14,96%</t>
+          <t>14,81%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>18,12%</t>
+          <t>17,99%</t>
         </is>
       </c>
     </row>
@@ -13753,12 +13753,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>35588</t>
+          <t>36147</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>56019</t>
+          <t>55789</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -13768,12 +13768,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>48,56%</t>
+          <t>49,33%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>76,44%</t>
+          <t>76,13%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -13788,12 +13788,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>51298</t>
+          <t>50702</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>65901</t>
+          <t>65474</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -13803,12 +13803,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>64,64%</t>
+          <t>63,88%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>83,03%</t>
+          <t>82,5%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -13823,12 +13823,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>91872</t>
+          <t>92024</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>117483</t>
+          <t>117169</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -13838,12 +13838,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>60,19%</t>
+          <t>60,29%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>76,96%</t>
+          <t>76,76%</t>
         </is>
       </c>
     </row>
@@ -13979,12 +13979,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>17263</t>
+          <t>17493</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>37694</t>
+          <t>37135</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -13994,12 +13994,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>23,56%</t>
+          <t>23,87%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>51,44%</t>
+          <t>50,67%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -14014,12 +14014,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>13465</t>
+          <t>13892</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>28068</t>
+          <t>28664</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -14029,12 +14029,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>16,97%</t>
+          <t>17,5%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>35,36%</t>
+          <t>36,12%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -14049,12 +14049,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>35165</t>
+          <t>35479</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>60776</t>
+          <t>60624</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -14064,12 +14064,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>23,04%</t>
+          <t>23,24%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>39,81%</t>
+          <t>39,71%</t>
         </is>
       </c>
     </row>
@@ -14209,12 +14209,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>100907</t>
+          <t>101298</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>118330</t>
+          <t>120015</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -14224,12 +14224,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>79,56%</t>
+          <t>79,86%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>93,29%</t>
+          <t>94,62%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -14244,12 +14244,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>103446</t>
+          <t>104355</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>118115</t>
+          <t>118017</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -14259,12 +14259,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>81,07%</t>
+          <t>81,79%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>92,57%</t>
+          <t>92,49%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -14279,12 +14279,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>211505</t>
+          <t>211123</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>233662</t>
+          <t>233039</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -14294,12 +14294,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>83,13%</t>
+          <t>82,98%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>91,84%</t>
+          <t>91,59%</t>
         </is>
       </c>
     </row>
@@ -14435,12 +14435,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>8509</t>
+          <t>6824</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>25932</t>
+          <t>25541</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -14450,12 +14450,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>20,44%</t>
+          <t>20,14%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -14470,12 +14470,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>9481</t>
+          <t>9579</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>24150</t>
+          <t>23241</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -14485,12 +14485,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>7,51%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>18,93%</t>
+          <t>18,21%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -14505,12 +14505,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>20773</t>
+          <t>21396</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>42930</t>
+          <t>43312</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -14520,12 +14520,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>8,41%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>16,87%</t>
+          <t>17,02%</t>
         </is>
       </c>
     </row>
@@ -14665,12 +14665,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>39297</t>
+          <t>39480</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>49272</t>
+          <t>49045</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -14680,12 +14680,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>68,29%</t>
+          <t>68,61%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>85,62%</t>
+          <t>85,23%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -14700,12 +14700,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>53156</t>
+          <t>53207</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>62192</t>
+          <t>62203</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -14715,12 +14715,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>79,14%</t>
+          <t>79,22%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>92,6%</t>
+          <t>92,62%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -14735,12 +14735,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>96237</t>
+          <t>95298</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>109715</t>
+          <t>109211</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>77,17%</t>
+          <t>76,42%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>87,98%</t>
+          <t>87,57%</t>
         </is>
       </c>
     </row>
@@ -14891,12 +14891,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>8273</t>
+          <t>8500</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>18248</t>
+          <t>18065</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -14906,12 +14906,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>14,38%</t>
+          <t>14,77%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>31,71%</t>
+          <t>31,39%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -14926,12 +14926,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>4971</t>
+          <t>4960</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>14007</t>
+          <t>13956</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -14941,12 +14941,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>7,38%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>20,86%</t>
+          <t>20,78%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -14961,12 +14961,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>14993</t>
+          <t>15497</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>28471</t>
+          <t>29410</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -14976,12 +14976,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>12,02%</t>
+          <t>12,43%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>22,83%</t>
+          <t>23,58%</t>
         </is>
       </c>
     </row>
@@ -15121,12 +15121,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>50890</t>
+          <t>51872</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>62738</t>
+          <t>63268</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -15136,12 +15136,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>72,55%</t>
+          <t>73,95%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>89,44%</t>
+          <t>90,2%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -15156,12 +15156,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>53775</t>
+          <t>54063</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>70999</t>
+          <t>70917</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -15171,12 +15171,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>68,82%</t>
+          <t>69,19%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>90,87%</t>
+          <t>90,76%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -15191,12 +15191,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>109320</t>
+          <t>111132</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>130722</t>
+          <t>131804</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -15206,12 +15206,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>73,73%</t>
+          <t>74,95%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>88,16%</t>
+          <t>88,89%</t>
         </is>
       </c>
     </row>
@@ -15347,12 +15347,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>7405</t>
+          <t>6875</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>19253</t>
+          <t>18271</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -15362,12 +15362,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>10,56%</t>
+          <t>9,8%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>27,45%</t>
+          <t>26,05%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -15382,12 +15382,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>7135</t>
+          <t>7217</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>24359</t>
+          <t>24071</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -15397,12 +15397,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>9,13%</t>
+          <t>9,24%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>31,18%</t>
+          <t>30,81%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -15417,12 +15417,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>17556</t>
+          <t>16474</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>38958</t>
+          <t>37146</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -15432,12 +15432,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>11,84%</t>
+          <t>11,11%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>26,27%</t>
+          <t>25,05%</t>
         </is>
       </c>
     </row>
@@ -15577,12 +15577,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>29227</t>
+          <t>30184</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>34053</t>
+          <t>34066</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -15592,12 +15592,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>84,69%</t>
+          <t>87,46%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>98,67%</t>
+          <t>98,7%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -15612,12 +15612,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>34624</t>
+          <t>34411</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>39694</t>
+          <t>39667</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -15627,12 +15627,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>85,03%</t>
+          <t>84,51%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>97,48%</t>
+          <t>97,42%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -15647,12 +15647,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>66962</t>
+          <t>66831</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>73129</t>
+          <t>73191</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -15662,12 +15662,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>89,01%</t>
+          <t>88,83%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>97,21%</t>
+          <t>97,29%</t>
         </is>
       </c>
     </row>
@@ -15803,12 +15803,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>460</t>
+          <t>447</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>5286</t>
+          <t>4329</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -15818,12 +15818,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>15,31%</t>
+          <t>12,54%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -15838,12 +15838,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1025</t>
+          <t>1052</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>6095</t>
+          <t>6308</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -15853,12 +15853,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>14,97%</t>
+          <t>15,49%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -15873,12 +15873,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2103</t>
+          <t>2041</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>8270</t>
+          <t>8401</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -15888,12 +15888,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>10,99%</t>
+          <t>11,17%</t>
         </is>
       </c>
     </row>
@@ -16033,12 +16033,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>35832</t>
+          <t>35972</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>42949</t>
+          <t>42899</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -16048,12 +16048,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>77,61%</t>
+          <t>77,92%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>93,03%</t>
+          <t>92,92%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -16068,12 +16068,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>41662</t>
+          <t>41840</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>51090</t>
+          <t>50846</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -16083,12 +16083,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>74,15%</t>
+          <t>74,47%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>90,93%</t>
+          <t>90,5%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -16103,12 +16103,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>80917</t>
+          <t>80901</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>92092</t>
+          <t>92590</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -16118,12 +16118,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>79,06%</t>
+          <t>79,04%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>89,97%</t>
+          <t>90,46%</t>
         </is>
       </c>
     </row>
@@ -16259,12 +16259,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3218</t>
+          <t>3268</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>10335</t>
+          <t>10195</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -16274,12 +16274,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>7,08%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>22,39%</t>
+          <t>22,08%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -16294,12 +16294,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>5096</t>
+          <t>5340</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>14524</t>
+          <t>14346</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -16309,12 +16309,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>9,07%</t>
+          <t>9,5%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>25,85%</t>
+          <t>25,53%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -16329,12 +16329,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>10261</t>
+          <t>9763</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>21436</t>
+          <t>21452</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -16344,12 +16344,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>10,03%</t>
+          <t>9,54%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>20,94%</t>
+          <t>20,96%</t>
         </is>
       </c>
     </row>
@@ -16489,12 +16489,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>88897</t>
+          <t>90956</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>106565</t>
+          <t>106772</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -16504,12 +16504,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>71,4%</t>
+          <t>73,05%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>85,59%</t>
+          <t>85,75%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -16524,7 +16524,7 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>105470</t>
+          <t>104489</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
@@ -16539,7 +16539,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>67,6%</t>
+          <t>66,98%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -16559,12 +16559,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>201372</t>
+          <t>201632</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>229370</t>
+          <t>228194</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -16574,12 +16574,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>71,79%</t>
+          <t>71,88%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>81,77%</t>
+          <t>81,35%</t>
         </is>
       </c>
     </row>
@@ -16715,12 +16715,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>17943</t>
+          <t>17736</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>35611</t>
+          <t>33552</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -16730,12 +16730,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>14,41%</t>
+          <t>14,25%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>28,6%</t>
+          <t>26,95%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -16755,7 +16755,7 @@
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>50542</t>
+          <t>51523</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -16770,7 +16770,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>32,4%</t>
+          <t>33,02%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -16785,12 +16785,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>51150</t>
+          <t>52326</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>79148</t>
+          <t>78888</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -16800,12 +16800,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>18,23%</t>
+          <t>18,65%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>28,21%</t>
+          <t>28,12%</t>
         </is>
       </c>
     </row>
@@ -16945,12 +16945,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>123974</t>
+          <t>122855</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>130007</t>
+          <t>129688</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -16960,12 +16960,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>94,19%</t>
+          <t>93,34%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>98,78%</t>
+          <t>98,53%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -16980,12 +16980,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>143058</t>
+          <t>143528</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>152965</t>
+          <t>153007</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -16995,12 +16995,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>91,24%</t>
+          <t>91,54%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>97,56%</t>
+          <t>97,58%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -17015,12 +17015,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>270921</t>
+          <t>271212</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>281751</t>
+          <t>282107</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -17030,12 +17030,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>93,93%</t>
+          <t>94,04%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>97,69%</t>
+          <t>97,81%</t>
         </is>
       </c>
     </row>
@@ -17171,12 +17171,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>1612</t>
+          <t>1931</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>7645</t>
+          <t>8764</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -17186,12 +17186,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>6,66%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -17206,12 +17206,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>3830</t>
+          <t>3788</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>13737</t>
+          <t>13267</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -17221,12 +17221,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>8,76%</t>
+          <t>8,46%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -17241,12 +17241,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>6663</t>
+          <t>6307</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>17493</t>
+          <t>17202</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -17256,12 +17256,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>5,96%</t>
         </is>
       </c>
     </row>
@@ -17401,12 +17401,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>540737</t>
+          <t>539979</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>580162</t>
+          <t>580609</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -17416,12 +17416,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>81,36%</t>
+          <t>81,25%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>87,29%</t>
+          <t>87,36%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -17436,12 +17436,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>623942</t>
+          <t>626659</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>662328</t>
+          <t>662355</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -17451,12 +17451,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>81,89%</t>
+          <t>82,24%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>86,92%</t>
+          <t>86,93%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -17471,12 +17471,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>1175066</t>
+          <t>1174859</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>1230418</t>
+          <t>1232167</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -17486,12 +17486,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>82,37%</t>
+          <t>82,35%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>86,25%</t>
+          <t>86,37%</t>
         </is>
       </c>
     </row>
@@ -17627,12 +17627,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>84455</t>
+          <t>84008</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>123880</t>
+          <t>124638</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -17642,12 +17642,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>12,71%</t>
+          <t>12,64%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>18,64%</t>
+          <t>18,75%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -17662,12 +17662,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>99644</t>
+          <t>99617</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>138030</t>
+          <t>135313</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -17677,12 +17677,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>13,08%</t>
+          <t>13,07%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>18,11%</t>
+          <t>17,76%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -17697,12 +17697,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>196171</t>
+          <t>194422</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>251523</t>
+          <t>251730</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -17712,12 +17712,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>13,75%</t>
+          <t>13,63%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>17,63%</t>
+          <t>17,65%</t>
         </is>
       </c>
     </row>
